--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54AB042-F7D5-42CD-B299-DB5F51E65251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2702796-8D3C-4B68-8506-CE561F357446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="124">
   <si>
     <t>LI1</t>
   </si>
@@ -365,36 +365,12 @@
     <t>Bitel@2026</t>
   </si>
   <si>
-    <t>USUARIO</t>
-  </si>
-  <si>
-    <t>CONTRASEÑA</t>
-  </si>
-  <si>
-    <t>PARTNER</t>
-  </si>
-  <si>
-    <t>BRANCH</t>
-  </si>
-  <si>
-    <t>BITEL ARE</t>
-  </si>
-  <si>
-    <t>BITEL CAJ</t>
-  </si>
-  <si>
-    <t>BITEL CUS</t>
-  </si>
-  <si>
     <t>TGI</t>
   </si>
   <si>
     <t>OS2005644345</t>
   </si>
   <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
     <t>VTP62146884</t>
   </si>
   <si>
@@ -408,13 +384,37 @@
   </si>
   <si>
     <t>vtp72437856</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>partner</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>user</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,11 +439,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -490,21 +485,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -513,8 +499,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -851,1008 +837,1222 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAE877-3225-4F66-BC9B-12054986298E}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="3"/>
+    <col min="4" max="4" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>515816</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="2">
-        <v>515816</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="E26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="E29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>515817</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="1">
-        <v>515817</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+      <c r="E32" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+      <c r="E33" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+      <c r="E34" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="E35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="E36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="E37" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+      <c r="E38" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+      <c r="E39" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
+      <c r="E40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="E41" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
+      <c r="E42" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
+      <c r="E43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
+      <c r="E44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+      <c r="E45" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="E46" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="E47" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="E48" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="E49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="E50" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>515950</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="1">
-        <v>515950</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
+      <c r="E51" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
+      <c r="E52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
+      <c r="E53" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
+      <c r="E54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+      <c r="E55" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+      <c r="E56" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+      <c r="E57" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
+      <c r="E58" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
+      <c r="E59" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="E60" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="E61" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="E62" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="E63" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="E64" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="E65" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
+      <c r="E66" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="E67" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="E68" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="E69" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
+      <c r="E70" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="E71" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2702796-8D3C-4B68-8506-CE561F357446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44F3E24-A383-4ADB-9A08-6B48D3FE2A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="126">
   <si>
     <t>LI1</t>
   </si>
@@ -170,9 +170,6 @@
     <t>LI7</t>
   </si>
   <si>
-    <t>MARCO</t>
-  </si>
-  <si>
     <t>OS272172034</t>
   </si>
   <si>
@@ -408,13 +405,22 @@
   </si>
   <si>
     <t>user</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>OS219333627</t>
+  </si>
+  <si>
+    <t>INTER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +453,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -485,7 +497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -502,6 +514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -837,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAE877-3225-4F66-BC9B-12054986298E}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -850,70 +863,70 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -921,50 +934,50 @@
         <v>515816</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -972,10 +985,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>0</v>
@@ -989,10 +1002,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>0</v>
@@ -1006,10 +1019,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>0</v>
@@ -1023,10 +1036,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>0</v>
@@ -1040,10 +1053,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>0</v>
@@ -1057,10 +1070,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>0</v>
@@ -1074,10 +1087,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>0</v>
@@ -1091,10 +1104,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>0</v>
@@ -1105,19 +1118,19 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1125,10 +1138,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>17</v>
@@ -1142,10 +1155,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>17</v>
@@ -1159,10 +1172,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>17</v>
@@ -1176,10 +1189,10 @@
         <v>23</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>17</v>
@@ -1193,10 +1206,10 @@
         <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>17</v>
@@ -1210,10 +1223,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>17</v>
@@ -1227,10 +1240,10 @@
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>17</v>
@@ -1244,10 +1257,10 @@
         <v>30</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>28</v>
@@ -1261,10 +1274,10 @@
         <v>31</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>28</v>
@@ -1273,49 +1286,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>35</v>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>34</v>
@@ -1326,84 +1339,84 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>515817</v>
-      </c>
       <c r="B32" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>47</v>
+      <c r="A33" s="1">
+        <v>515817</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>15</v>
@@ -1411,16 +1424,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>15</v>
@@ -1428,84 +1441,84 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>15</v>
@@ -1513,16 +1526,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>15</v>
@@ -1530,16 +1543,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>15</v>
@@ -1547,16 +1560,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>15</v>
@@ -1564,16 +1577,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>15</v>
@@ -1581,16 +1594,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>15</v>
@@ -1598,16 +1611,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>15</v>
@@ -1615,118 +1628,118 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="B51" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>515950</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="B52" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>15</v>
@@ -1734,16 +1747,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>15</v>
@@ -1751,16 +1764,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>15</v>
@@ -1768,16 +1781,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>15</v>
@@ -1785,16 +1798,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>15</v>
@@ -1802,16 +1815,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>15</v>
@@ -1819,16 +1832,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>15</v>
@@ -1836,16 +1849,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>15</v>
@@ -1853,118 +1866,118 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>15</v>
@@ -1972,87 +1985,104 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>106</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44F3E24-A383-4ADB-9A08-6B48D3FE2A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9109CA7F-C8EA-4D77-8945-7BB0884CF559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="136">
   <si>
     <t>LI1</t>
   </si>
@@ -62,365 +62,395 @@
     <t>OS276633211</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>OS260957595</t>
+  </si>
+  <si>
+    <t>TECNICON</t>
+  </si>
+  <si>
+    <t>OS210146724</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>BITEL</t>
+  </si>
+  <si>
+    <t>OS206467526</t>
+  </si>
+  <si>
+    <t>LI2</t>
+  </si>
+  <si>
+    <t>OS172702795</t>
+  </si>
+  <si>
+    <t>OS271803944</t>
+  </si>
+  <si>
+    <t>CEMI</t>
+  </si>
+  <si>
+    <t>OS240300451</t>
+  </si>
+  <si>
+    <t>CHRISTIAN</t>
+  </si>
+  <si>
+    <t>OS243248884</t>
+  </si>
+  <si>
+    <t>LOMATEL</t>
+  </si>
+  <si>
+    <t>OS276314436</t>
+  </si>
+  <si>
+    <t>DIJUSA</t>
+  </si>
+  <si>
+    <t>OS246580939</t>
+  </si>
+  <si>
+    <t>LI3</t>
+  </si>
+  <si>
+    <t>ALLIZ</t>
+  </si>
+  <si>
+    <t>OS270404519</t>
+  </si>
+  <si>
+    <t>VTP72899176</t>
+  </si>
+  <si>
+    <t>OS245469163</t>
+  </si>
+  <si>
+    <t>ERAM</t>
+  </si>
+  <si>
+    <t>LI4</t>
+  </si>
+  <si>
+    <t>VTP60073992</t>
+  </si>
+  <si>
+    <t>BROKERS</t>
+  </si>
+  <si>
+    <t>OS209909578</t>
+  </si>
+  <si>
+    <t>OS273510490</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>OS207467274</t>
+  </si>
+  <si>
+    <t>SUNQUNET</t>
+  </si>
+  <si>
+    <t>OS210754583</t>
+  </si>
+  <si>
+    <t>LI7</t>
+  </si>
+  <si>
+    <t>OS272172034</t>
+  </si>
+  <si>
+    <t>ARE</t>
+  </si>
+  <si>
+    <t>OS145842206</t>
+  </si>
+  <si>
+    <t>OS272907286</t>
+  </si>
+  <si>
+    <t>CORPCRAS</t>
+  </si>
+  <si>
+    <t>OS276970175</t>
+  </si>
+  <si>
+    <t>MOSTBE</t>
+  </si>
+  <si>
+    <t>OS274034825</t>
+  </si>
+  <si>
+    <t>OS244604729</t>
+  </si>
+  <si>
+    <t>PERU-BUSSINESS</t>
+  </si>
+  <si>
+    <t>CAJ</t>
+  </si>
+  <si>
+    <t>OS345084149</t>
+  </si>
+  <si>
+    <t>OS371839813</t>
+  </si>
+  <si>
+    <t>OS373058822</t>
+  </si>
+  <si>
+    <t>OS373266099</t>
+  </si>
+  <si>
+    <t>OS373435764</t>
+  </si>
+  <si>
+    <t>VTP45451818</t>
+  </si>
+  <si>
+    <t>OS375652472</t>
+  </si>
+  <si>
+    <t>CUS</t>
+  </si>
+  <si>
+    <t>OS241236936</t>
+  </si>
+  <si>
+    <t>ELIM</t>
+  </si>
+  <si>
+    <t>OS276171264</t>
+  </si>
+  <si>
+    <t>LABTELL</t>
+  </si>
+  <si>
+    <t>OS275928004</t>
+  </si>
+  <si>
+    <t>MUNAY</t>
+  </si>
+  <si>
+    <t>OS276330539</t>
+  </si>
+  <si>
+    <t>TECNORED</t>
+  </si>
+  <si>
+    <t>OS242022647</t>
+  </si>
+  <si>
+    <t>ZOMITECH</t>
+  </si>
+  <si>
+    <t>OS242269048</t>
+  </si>
+  <si>
+    <t>HUN</t>
+  </si>
+  <si>
+    <t>OS145989938</t>
+  </si>
+  <si>
+    <t>OS148037792</t>
+  </si>
+  <si>
+    <t>OS170227756</t>
+  </si>
+  <si>
+    <t>OS172757064</t>
+  </si>
+  <si>
+    <t>OS246679085</t>
+  </si>
+  <si>
+    <t>OS247245274</t>
+  </si>
+  <si>
+    <t>VTP21257961</t>
+  </si>
+  <si>
+    <t>JUN</t>
+  </si>
+  <si>
+    <t>VTP42682885</t>
+  </si>
+  <si>
+    <t>L&amp;P</t>
+  </si>
+  <si>
+    <t>OS271496792</t>
+  </si>
+  <si>
+    <t>SIMEC</t>
+  </si>
+  <si>
+    <t>OS261632370</t>
+  </si>
+  <si>
+    <t>LAL</t>
+  </si>
+  <si>
+    <t>VTP70285050</t>
+  </si>
+  <si>
+    <t>DALU</t>
+  </si>
+  <si>
+    <t>OS240073698</t>
+  </si>
+  <si>
+    <t>M&amp;P</t>
+  </si>
+  <si>
+    <t>OS276549646</t>
+  </si>
+  <si>
+    <t>PIU</t>
+  </si>
+  <si>
+    <t>OS176218875</t>
+  </si>
+  <si>
+    <t>VTP40291743</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>OS202872987</t>
+  </si>
+  <si>
+    <t>JFLOWERS</t>
+  </si>
+  <si>
+    <t>OS202802542</t>
+  </si>
+  <si>
+    <t>JYS</t>
+  </si>
+  <si>
+    <t>OS240244251</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>OS244738090</t>
+  </si>
+  <si>
+    <t>GYM</t>
+  </si>
+  <si>
+    <t>OS170160673</t>
+  </si>
+  <si>
+    <t>Bitel@2026</t>
+  </si>
+  <si>
+    <t>TGI</t>
+  </si>
+  <si>
+    <t>OS2005644345</t>
+  </si>
+  <si>
+    <t>VTP62146884</t>
+  </si>
+  <si>
+    <t>VTP76066116</t>
+  </si>
+  <si>
+    <t>VTP74746195</t>
+  </si>
+  <si>
+    <t>VTP72925383</t>
+  </si>
+  <si>
+    <t>vtp72437856</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>partner</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>OS219333627</t>
+  </si>
+  <si>
+    <t>INTER</t>
+  </si>
+  <si>
+    <t>OS271034236</t>
+  </si>
+  <si>
     <t>MYS</t>
   </si>
   <si>
-    <t>OS271034236</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>OS260957595</t>
-  </si>
-  <si>
-    <t>TECNICON</t>
-  </si>
-  <si>
-    <t>OS210146724</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>BITEL</t>
-  </si>
-  <si>
-    <t>OS206467526</t>
-  </si>
-  <si>
-    <t>LI2</t>
-  </si>
-  <si>
-    <t>OS172702795</t>
-  </si>
-  <si>
-    <t>OS271803944</t>
-  </si>
-  <si>
-    <t>CEMI</t>
-  </si>
-  <si>
-    <t>OS240300451</t>
-  </si>
-  <si>
-    <t>CHRISTIAN</t>
-  </si>
-  <si>
-    <t>OS243248884</t>
-  </si>
-  <si>
-    <t>LOMATEL</t>
-  </si>
-  <si>
-    <t>OS276314436</t>
-  </si>
-  <si>
-    <t>DIJUSA</t>
-  </si>
-  <si>
-    <t>OS246580939</t>
-  </si>
-  <si>
-    <t>LI3</t>
-  </si>
-  <si>
-    <t>ALLIZ</t>
-  </si>
-  <si>
-    <t>OS270404519</t>
-  </si>
-  <si>
-    <t>VTP72899176</t>
-  </si>
-  <si>
-    <t>OS245469163</t>
-  </si>
-  <si>
-    <t>ERAM</t>
-  </si>
-  <si>
-    <t>LI4</t>
-  </si>
-  <si>
-    <t>VTP60073992</t>
-  </si>
-  <si>
-    <t>BROKERS</t>
-  </si>
-  <si>
-    <t>OS209909578</t>
-  </si>
-  <si>
-    <t>OS273510490</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>OS207467274</t>
-  </si>
-  <si>
-    <t>SUNQUNET</t>
-  </si>
-  <si>
-    <t>OS210754583</t>
-  </si>
-  <si>
-    <t>LI7</t>
-  </si>
-  <si>
-    <t>OS272172034</t>
-  </si>
-  <si>
-    <t>ARE</t>
-  </si>
-  <si>
-    <t>OS145842206</t>
-  </si>
-  <si>
-    <t>OS272907286</t>
-  </si>
-  <si>
-    <t>CORPCRAS</t>
-  </si>
-  <si>
-    <t>OS276970175</t>
-  </si>
-  <si>
-    <t>MOSTBE</t>
-  </si>
-  <si>
-    <t>OS274034825</t>
-  </si>
-  <si>
-    <t>OS244604729</t>
-  </si>
-  <si>
-    <t>PERU-BUSSINESS</t>
-  </si>
-  <si>
-    <t>CAJ</t>
-  </si>
-  <si>
-    <t>OS345084149</t>
-  </si>
-  <si>
-    <t>OS371839813</t>
-  </si>
-  <si>
-    <t>OS373058822</t>
-  </si>
-  <si>
-    <t>OS373266099</t>
-  </si>
-  <si>
-    <t>OS373435764</t>
-  </si>
-  <si>
-    <t>VTP45451818</t>
-  </si>
-  <si>
-    <t>OS375652472</t>
-  </si>
-  <si>
-    <t>CUS</t>
-  </si>
-  <si>
-    <t>OS241236936</t>
-  </si>
-  <si>
-    <t>ELIM</t>
-  </si>
-  <si>
-    <t>OS276171264</t>
-  </si>
-  <si>
-    <t>LABTELL</t>
-  </si>
-  <si>
-    <t>OS275928004</t>
-  </si>
-  <si>
-    <t>MUNAY</t>
-  </si>
-  <si>
-    <t>OS276330539</t>
-  </si>
-  <si>
-    <t>TECNORED</t>
-  </si>
-  <si>
-    <t>OS242022647</t>
-  </si>
-  <si>
-    <t>ZOMITECH</t>
-  </si>
-  <si>
-    <t>OS242269048</t>
-  </si>
-  <si>
-    <t>HUN</t>
-  </si>
-  <si>
-    <t>OS145989938</t>
-  </si>
-  <si>
-    <t>OS148037792</t>
-  </si>
-  <si>
-    <t>OS170227756</t>
-  </si>
-  <si>
-    <t>OS172757064</t>
-  </si>
-  <si>
-    <t>OS246679085</t>
-  </si>
-  <si>
-    <t>OS247245274</t>
-  </si>
-  <si>
-    <t>VTP21257961</t>
-  </si>
-  <si>
-    <t>JUN</t>
-  </si>
-  <si>
-    <t>VTP42682885</t>
-  </si>
-  <si>
-    <t>L&amp;P</t>
-  </si>
-  <si>
-    <t>OS271496792</t>
-  </si>
-  <si>
-    <t>SIMEC</t>
-  </si>
-  <si>
-    <t>OS261632370</t>
-  </si>
-  <si>
-    <t>LAL</t>
-  </si>
-  <si>
-    <t>VTP70285050</t>
-  </si>
-  <si>
-    <t>DALU</t>
-  </si>
-  <si>
-    <t>OS240073698</t>
-  </si>
-  <si>
-    <t>M&amp;P</t>
-  </si>
-  <si>
-    <t>OS276549646</t>
-  </si>
-  <si>
-    <t>PIU</t>
-  </si>
-  <si>
-    <t>OS176218875</t>
-  </si>
-  <si>
-    <t>VTP40291743</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>OS202872987</t>
-  </si>
-  <si>
-    <t>JFLOWERS</t>
-  </si>
-  <si>
-    <t>OS202802542</t>
-  </si>
-  <si>
-    <t>JYS</t>
-  </si>
-  <si>
-    <t>OS240244251</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
-    <t>OS244738090</t>
-  </si>
-  <si>
-    <t>GYM</t>
-  </si>
-  <si>
-    <t>OS170160673</t>
-  </si>
-  <si>
-    <t>Bitel@2026</t>
-  </si>
-  <si>
-    <t>TGI</t>
-  </si>
-  <si>
-    <t>OS2005644345</t>
-  </si>
-  <si>
-    <t>VTP62146884</t>
-  </si>
-  <si>
-    <t>VTP76066116</t>
-  </si>
-  <si>
-    <t>VTP74746195</t>
-  </si>
-  <si>
-    <t>VTP72925383</t>
-  </si>
-  <si>
-    <t>vtp72437856</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>branch</t>
-  </si>
-  <si>
-    <t>partner</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>OS219333627</t>
-  </si>
-  <si>
-    <t>INTER</t>
+    <t>GARATIAS LIMA</t>
+  </si>
+  <si>
+    <t>CANCELADOS</t>
+  </si>
+  <si>
+    <t>ONLINE LIMA</t>
+  </si>
+  <si>
+    <t>PENDIENTES ODN</t>
+  </si>
+  <si>
+    <t>LI1 TGI</t>
+  </si>
+  <si>
+    <t>access 1</t>
+  </si>
+  <si>
+    <t>access 2</t>
+  </si>
+  <si>
+    <t>access 3</t>
+  </si>
+  <si>
+    <t>access 4</t>
+  </si>
+  <si>
+    <t>access 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,6 +489,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -850,145 +886,164 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAE877-3225-4F66-BC9B-12054986298E}">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="3"/>
-    <col min="4" max="4" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="3"/>
+    <col min="6" max="6" width="14" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>515816</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>0</v>
@@ -996,16 +1051,19 @@
       <c r="E8" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>0</v>
@@ -1013,16 +1071,19 @@
       <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>0</v>
@@ -1030,379 +1091,412 @@
       <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1410,322 +1504,322 @@
         <v>515817</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,359 +1827,360 @@
         <v>515950</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9109CA7F-C8EA-4D77-8945-7BB0884CF559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A910E1F-42C5-4D70-B063-4B68D4C18056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="143">
   <si>
     <t>LI1</t>
   </si>
@@ -444,6 +444,27 @@
   </si>
   <si>
     <t>access 5</t>
+  </si>
+  <si>
+    <t>LI2 ERAM</t>
+  </si>
+  <si>
+    <t>LI2 DIJUSA</t>
+  </si>
+  <si>
+    <t>LI3 INTER</t>
+  </si>
+  <si>
+    <t>access 6</t>
+  </si>
+  <si>
+    <t>LI4 TGI</t>
+  </si>
+  <si>
+    <t>LI4 BROKERS</t>
+  </si>
+  <si>
+    <t>LI7 MARCOS</t>
   </si>
 </sst>
 </file>
@@ -886,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAE877-3225-4F66-BC9B-12054986298E}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -898,10 +919,12 @@
     <col min="7" max="7" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.42578125" style="3"/>
+    <col min="10" max="10" width="11.42578125" style="3"/>
+    <col min="11" max="11" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>115</v>
       </c>
@@ -932,8 +955,11 @@
       <c r="J1" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>108</v>
       </c>
@@ -950,7 +976,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
@@ -967,7 +993,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
@@ -984,7 +1010,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>515816</v>
       </c>
@@ -1001,7 +1027,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>111</v>
       </c>
@@ -1018,7 +1044,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -1035,7 +1061,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -1055,7 +1081,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1101,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,7 +1121,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1115,7 +1141,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -1135,7 +1161,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1155,7 +1181,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1175,7 +1201,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,7 +1233,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>107</v>
       </c>
@@ -1226,8 +1252,11 @@
       <c r="F16" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G16" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1243,8 +1272,26 @@
       <c r="E17" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1260,8 +1307,26 @@
       <c r="E18" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1277,8 +1342,11 @@
       <c r="E19" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -1294,8 +1362,11 @@
       <c r="E20" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -1311,8 +1382,11 @@
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1328,8 +1402,11 @@
       <c r="E22" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -1345,8 +1422,11 @@
       <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
@@ -1362,8 +1442,11 @@
       <c r="E24" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1379,8 +1462,23 @@
       <c r="E25" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>122</v>
       </c>
@@ -1396,8 +1494,11 @@
       <c r="E26" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1413,8 +1514,26 @@
       <c r="E27" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1430,8 +1549,14 @@
       <c r="E28" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -1447,8 +1572,14 @@
       <c r="E29" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -1464,8 +1595,11 @@
       <c r="E30" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -1481,8 +1615,11 @@
       <c r="E31" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>42</v>
       </c>
@@ -1498,8 +1635,14 @@
       <c r="E32" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>515817</v>
       </c>
@@ -1515,8 +1658,23 @@
       <c r="E33" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>44</v>
       </c>
@@ -1533,7 +1691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
@@ -1550,7 +1708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
@@ -1567,7 +1725,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>49</v>
       </c>
@@ -1584,7 +1742,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -1601,7 +1759,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>53</v>
       </c>
@@ -1618,7 +1776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>54</v>
       </c>
@@ -1635,7 +1793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>55</v>
       </c>
@@ -1652,7 +1810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -1669,7 +1827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>57</v>
       </c>
@@ -1686,7 +1844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>58</v>
       </c>
@@ -1703,7 +1861,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>59</v>
       </c>
@@ -1720,7 +1878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>61</v>
       </c>
@@ -1737,7 +1895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
@@ -1754,7 +1912,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>65</v>
       </c>

--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A910E1F-42C5-4D70-B063-4B68D4C18056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FD367E-29D7-41F2-B450-B9FAFA30BFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="145">
   <si>
     <t>LI1</t>
   </si>
@@ -416,9 +416,6 @@
     <t>MYS</t>
   </si>
   <si>
-    <t>GARATIAS LIMA</t>
-  </si>
-  <si>
     <t>CANCELADOS</t>
   </si>
   <si>
@@ -465,6 +462,15 @@
   </si>
   <si>
     <t>LI7 MARCOS</t>
+  </si>
+  <si>
+    <t>GARANTIAS PROVINCIA</t>
+  </si>
+  <si>
+    <t>FUERA DE GARANTÍA PROVINCIA</t>
+  </si>
+  <si>
+    <t>GARANTIAS LIMA</t>
   </si>
 </sst>
 </file>
@@ -554,7 +560,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -572,6 +578,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -915,8 +924,7 @@
     <col min="3" max="3" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="29.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" style="3"/>
@@ -941,22 +949,22 @@
         <v>117</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1078,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1098,7 +1106,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1118,14 +1126,14 @@
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1138,7 +1146,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1158,7 +1166,7 @@
         <v>125</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1178,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1198,7 +1206,7 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1218,19 +1226,19 @@
         <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1250,10 +1258,10 @@
         <v>106</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1273,22 +1281,22 @@
         <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1308,22 +1316,22 @@
         <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1343,7 +1351,7 @@
         <v>18</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1363,7 +1371,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1383,7 +1391,7 @@
         <v>22</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1403,7 +1411,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1423,7 +1431,7 @@
         <v>31</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1443,7 +1451,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,19 +1471,19 @@
         <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -1495,7 +1503,7 @@
         <v>123</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1515,22 +1523,22 @@
         <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1550,10 +1558,10 @@
         <v>34</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1573,10 +1581,10 @@
         <v>34</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1596,7 +1604,7 @@
         <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1616,7 +1624,7 @@
         <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,10 +1644,10 @@
         <v>121</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1659,19 +1667,19 @@
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="I33" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1690,6 +1698,12 @@
       <c r="E34" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1707,6 +1721,12 @@
       <c r="E35" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F35" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -1724,6 +1744,9 @@
       <c r="E36" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F36" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -1741,6 +1764,9 @@
       <c r="E37" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="F37" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -1758,6 +1784,9 @@
       <c r="E38" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="F38" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -1775,6 +1804,9 @@
       <c r="E39" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F39" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -1792,6 +1824,9 @@
       <c r="E40" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F40" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -1809,6 +1844,9 @@
       <c r="E41" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F41" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -1826,6 +1864,9 @@
       <c r="E42" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F42" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -1843,6 +1884,9 @@
       <c r="E43" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F43" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
@@ -1860,6 +1904,9 @@
       <c r="E44" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F44" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -1877,6 +1924,9 @@
       <c r="E45" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F45" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -1894,6 +1944,12 @@
       <c r="E46" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="F46" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -1911,6 +1967,12 @@
       <c r="E47" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="F47" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
@@ -1928,8 +1990,14 @@
       <c r="E48" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>67</v>
       </c>
@@ -1945,8 +2013,14 @@
       <c r="E49" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>69</v>
       </c>
@@ -1962,8 +2036,14 @@
       <c r="E50" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>71</v>
       </c>
@@ -1979,8 +2059,14 @@
       <c r="E51" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>515950</v>
       </c>
@@ -1996,8 +2082,14 @@
       <c r="E52" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
@@ -2013,8 +2105,11 @@
       <c r="E53" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>74</v>
       </c>
@@ -2030,8 +2125,11 @@
       <c r="E54" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>75</v>
       </c>
@@ -2047,8 +2145,11 @@
       <c r="E55" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>76</v>
       </c>
@@ -2064,8 +2165,11 @@
       <c r="E56" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>77</v>
       </c>
@@ -2081,8 +2185,11 @@
       <c r="E57" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>78</v>
       </c>
@@ -2098,8 +2205,11 @@
       <c r="E58" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>79</v>
       </c>
@@ -2115,8 +2225,11 @@
       <c r="E59" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>81</v>
       </c>
@@ -2132,8 +2245,14 @@
       <c r="E60" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>83</v>
       </c>
@@ -2149,8 +2268,11 @@
       <c r="E61" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>85</v>
       </c>
@@ -2166,8 +2288,11 @@
       <c r="E62" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>87</v>
       </c>
@@ -2183,8 +2308,14 @@
       <c r="E63" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>89</v>
       </c>
@@ -2200,8 +2331,14 @@
       <c r="E64" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>91</v>
       </c>
@@ -2217,8 +2354,14 @@
       <c r="E65" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>93</v>
       </c>
@@ -2234,8 +2377,14 @@
       <c r="E66" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>94</v>
       </c>
@@ -2251,8 +2400,14 @@
       <c r="E67" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>96</v>
       </c>
@@ -2268,8 +2423,11 @@
       <c r="E68" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>98</v>
       </c>
@@ -2285,8 +2443,11 @@
       <c r="E69" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>100</v>
       </c>
@@ -2302,8 +2463,11 @@
       <c r="E70" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>102</v>
       </c>
@@ -2319,8 +2483,14 @@
       <c r="E71" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>104</v>
       </c>
@@ -2336,9 +2506,16 @@
       <c r="E72" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="F72" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B11" r:id="rId1" xr:uid="{46437A8E-B625-462E-A349-14AE4F0FBC3E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FD367E-29D7-41F2-B450-B9FAFA30BFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7342970-5E87-416B-B33E-E4E841785208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="16305" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1261,7 +1261,7 @@
         <v>129</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">

--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7342970-5E87-416B-B33E-E4E841785208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E61495-333C-4B05-B1A2-7AEC0411F56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="16305" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="147">
   <si>
     <t>LI1</t>
   </si>
@@ -308,9 +308,6 @@
     <t>OS240073698</t>
   </si>
   <si>
-    <t>M&amp;P</t>
-  </si>
-  <si>
     <t>OS276549646</t>
   </si>
   <si>
@@ -471,6 +468,15 @@
   </si>
   <si>
     <t>GARANTIAS LIMA</t>
+  </si>
+  <si>
+    <t>access 7</t>
+  </si>
+  <si>
+    <t>DESPLIEGUE</t>
+  </si>
+  <si>
+    <t>MYP</t>
   </si>
 </sst>
 </file>
@@ -916,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAE877-3225-4F66-BC9B-12054986298E}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -932,152 +938,155 @@
     <col min="12" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>515816</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>0</v>
@@ -1086,18 +1095,21 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>0</v>
@@ -1106,18 +1118,21 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>0</v>
@@ -1126,18 +1141,21 @@
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>0</v>
@@ -1146,38 +1164,44 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>0</v>
@@ -1186,18 +1210,21 @@
         <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>0</v>
@@ -1206,18 +1233,21 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>0</v>
@@ -1226,53 +1256,56 @@
         <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
@@ -1281,33 +1314,36 @@
         <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>15</v>
@@ -1316,33 +1352,36 @@
         <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>15</v>
@@ -1351,18 +1390,21 @@
         <v>18</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>15</v>
@@ -1371,18 +1413,21 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>15</v>
@@ -1391,18 +1436,21 @@
         <v>22</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>15</v>
@@ -1411,18 +1459,21 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>15</v>
@@ -1431,18 +1482,21 @@
         <v>31</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>26</v>
@@ -1451,18 +1505,21 @@
         <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>26</v>
@@ -1471,50 +1528,56 @@
         <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -1523,33 +1586,36 @@
         <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>32</v>
@@ -1558,21 +1624,24 @@
         <v>34</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>32</v>
@@ -1581,21 +1650,24 @@
         <v>34</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>32</v>
@@ -1604,18 +1676,21 @@
         <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>32</v>
@@ -1624,41 +1699,47 @@
         <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>515817</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>41</v>
@@ -1667,30 +1748,33 @@
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="I33" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>43</v>
@@ -1699,21 +1783,24 @@
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>43</v>
@@ -1722,21 +1809,24 @@
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>43</v>
@@ -1745,18 +1835,21 @@
         <v>46</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>43</v>
@@ -1765,18 +1858,21 @@
         <v>48</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>43</v>
@@ -1785,18 +1881,21 @@
         <v>51</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>52</v>
@@ -1805,18 +1904,21 @@
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>52</v>
@@ -1825,18 +1927,21 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>52</v>
@@ -1845,18 +1950,21 @@
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>52</v>
@@ -1865,18 +1973,21 @@
         <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>52</v>
@@ -1885,18 +1996,21 @@
         <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>52</v>
@@ -1905,18 +2019,21 @@
         <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>52</v>
@@ -1925,18 +2042,21 @@
         <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>60</v>
@@ -1945,21 +2065,24 @@
         <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>60</v>
@@ -1968,21 +2091,24 @@
         <v>62</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>60</v>
@@ -1991,21 +2117,24 @@
         <v>64</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>60</v>
@@ -2014,21 +2143,24 @@
         <v>66</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>60</v>
@@ -2037,21 +2169,24 @@
         <v>68</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>60</v>
@@ -2060,21 +2195,24 @@
         <v>70</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>515950</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>60</v>
@@ -2083,21 +2221,24 @@
         <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>72</v>
@@ -2106,18 +2247,21 @@
         <v>13</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>72</v>
@@ -2126,18 +2270,21 @@
         <v>13</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>72</v>
@@ -2146,18 +2293,21 @@
         <v>13</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>72</v>
@@ -2166,18 +2316,21 @@
         <v>13</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>72</v>
@@ -2186,18 +2339,21 @@
         <v>13</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>72</v>
@@ -2206,18 +2362,21 @@
         <v>13</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>72</v>
@@ -2226,18 +2385,21 @@
         <v>13</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>80</v>
@@ -2246,21 +2408,24 @@
         <v>13</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>80</v>
@@ -2269,18 +2434,21 @@
         <v>82</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>80</v>
@@ -2289,18 +2457,21 @@
         <v>84</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>86</v>
@@ -2309,21 +2480,24 @@
         <v>13</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>86</v>
@@ -2332,182 +2506,206 @@
         <v>88</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B67" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="F68" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="F69" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="F70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="E71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="F72" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E61495-333C-4B05-B1A2-7AEC0411F56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BDD617-41B5-4D32-9C4E-F5011291315C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="148">
   <si>
     <t>LI1</t>
   </si>
@@ -477,6 +477,9 @@
   </si>
   <si>
     <t>MYP</t>
+  </si>
+  <si>
+    <t>VTP43081679</t>
   </si>
 </sst>
 </file>
@@ -922,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAE877-3225-4F66-BC9B-12054986298E}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -2708,6 +2711,26 @@
         <v>141</v>
       </c>
     </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/STAFF.xlsx
+++ b/STAFF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjvar\Downloads\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BDD617-41B5-4D32-9C4E-F5011291315C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573CCC0B-56F4-4C6A-90C7-99CD37D3E0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9F33A6-51F6-4C4E-B97B-768C0FAFCB01}"/>
   </bookViews>
@@ -2715,7 +2715,7 @@
       <c r="A73" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C73" s="5" t="s">
@@ -2735,8 +2735,9 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B11" r:id="rId1" xr:uid="{46437A8E-B625-462E-A349-14AE4F0FBC3E}"/>
+    <hyperlink ref="B73" r:id="rId2" xr:uid="{F2CE10C1-BAF3-42B2-B537-137CB8F2BB25}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>